--- a/translation-matrix.xlsx
+++ b/translation-matrix.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="589">
   <si>
     <t xml:space="preserve">var</t>
   </si>
@@ -785,6 +785,12 @@
   </si>
   <si>
     <t xml:space="preserve">Alvo(s) da política</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_bezos_ecu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivo del GBF</t>
   </si>
   <si>
     <t xml:space="preserve">policy_bezos_per</t>
@@ -2000,9 +2006,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1048576"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="36.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
   </cols>
@@ -3735,28 +3741,18 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>263</v>
-      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -3779,25 +3775,25 @@
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="G45" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -3819,22 +3815,28 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -3855,22 +3857,22 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="B47" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E47" s="4"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
-        <v>275</v>
-      </c>
+      <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -3893,19 +3895,19 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -3927,27 +3929,21 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -3969,21 +3965,27 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="G50" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -4005,21 +4007,21 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -4043,18 +4045,20 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+      <c r="G52" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -4075,28 +4079,20 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>297</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -4117,21 +4113,27 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="G54" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -4153,27 +4155,21 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -4195,27 +4191,27 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="F56" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="G56" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -4239,19 +4235,25 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="G57" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -4273,20 +4275,22 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4307,26 +4311,20 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>330</v>
-      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2" t="s">
-        <v>328</v>
-      </c>
+      <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4347,27 +4345,25 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="E60" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>336</v>
-      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -4389,27 +4385,27 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="G61" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -4431,27 +4427,27 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="G62" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -4473,22 +4469,28 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4509,18 +4511,18 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -4546,27 +4548,21 @@
       <c r="Z64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>366</v>
-      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4587,27 +4583,27 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="G66" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -4629,27 +4625,27 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="G67" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4671,27 +4667,27 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="G68" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4714,24 +4710,26 @@
       <c r="Z68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -4753,21 +4751,25 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -4789,21 +4791,21 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -4825,21 +4827,21 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -4861,27 +4863,21 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>409</v>
-      </c>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -4903,21 +4899,27 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -4941,23 +4943,19 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>418</v>
-      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -4979,25 +4977,25 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -5019,27 +5017,25 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="F77" s="2"/>
+      <c r="G77" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -5061,23 +5057,27 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="78" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -5099,27 +5099,23 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -5141,27 +5137,27 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="G80" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -5183,27 +5179,27 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="G81" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -5225,27 +5221,27 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="G82" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -5269,25 +5265,25 @@
     </row>
     <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="G83" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -5311,25 +5307,25 @@
     </row>
     <row r="84" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="F84" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="G84" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -5353,25 +5349,25 @@
     </row>
     <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="G85" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -5393,23 +5389,27 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
+    <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
       <c r="G86" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -5431,27 +5431,23 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -5473,19 +5469,27 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
+    <row r="88" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
@@ -5507,27 +5511,19 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
@@ -5551,25 +5547,25 @@
     </row>
     <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="G90" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
@@ -5591,19 +5587,27 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
+    <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
@@ -5627,17 +5631,17 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
@@ -5659,27 +5663,19 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -5703,25 +5699,25 @@
     </row>
     <row r="94" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="F94" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="G94" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -5743,20 +5739,28 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="F95" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="D95" s="6"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
+      <c r="G95" s="2" t="s">
+        <v>528</v>
+      </c>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
@@ -5777,20 +5781,20 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+    <row r="96" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="4"/>
       <c r="F96" s="2"/>
-      <c r="G96" s="2" t="s">
-        <v>535</v>
-      </c>
+      <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
@@ -5811,16 +5815,20 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
+      <c r="G97" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
@@ -5841,24 +5849,16 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B98" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>540</v>
-      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="2" t="s">
-        <v>541</v>
-      </c>
+      <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
@@ -5879,27 +5879,23 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+    <row r="99" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -5923,25 +5919,25 @@
     </row>
     <row r="100" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="G100" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -5963,27 +5959,27 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E101" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="F101" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="G101" s="2" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -6005,25 +6001,27 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
+    <row r="102" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
@@ -6045,25 +6043,25 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
@@ -6087,23 +6085,23 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
@@ -6125,27 +6123,25 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="F105" s="2"/>
+      <c r="G105" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -6167,14 +6163,28 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
+    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>588</v>
+      </c>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
@@ -31787,13 +31797,40 @@
       <c r="Y1020" s="2"/>
       <c r="Z1020" s="2"/>
     </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1021" s="2"/>
+      <c r="B1021" s="2"/>
+      <c r="C1021" s="2"/>
+      <c r="D1021" s="2"/>
+      <c r="E1021" s="2"/>
+      <c r="F1021" s="2"/>
+      <c r="G1021" s="2"/>
+      <c r="H1021" s="2"/>
+      <c r="I1021" s="2"/>
+      <c r="J1021" s="2"/>
+      <c r="K1021" s="2"/>
+      <c r="L1021" s="2"/>
+      <c r="M1021" s="2"/>
+      <c r="N1021" s="2"/>
+      <c r="O1021" s="2"/>
+      <c r="P1021" s="2"/>
+      <c r="Q1021" s="2"/>
+      <c r="R1021" s="2"/>
+      <c r="S1021" s="2"/>
+      <c r="T1021" s="2"/>
+      <c r="U1021" s="2"/>
+      <c r="V1021" s="2"/>
+      <c r="W1021" s="2"/>
+      <c r="X1021" s="2"/>
+      <c r="Y1021" s="2"/>
+      <c r="Z1021" s="2"/>
+    </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:L153">
+  <conditionalFormatting sqref="A2:L154">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
